--- a/assessment_forms/024_supply_chain_operations_assessment--assessment_forms.xlsx
+++ b/assessment_forms/024_supply_chain_operations_assessment--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,18 +520,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>supply_chain_operations</t>
+          <t>overall_risk</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>supply_chain_operations</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is the overall risk of your supply chain operations?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please describe the overall risk of your supply chain operations.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,64 +547,76 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>overall_risk</t>
+          <t>reporting_team</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>overall_risk</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What is the name of your reporting team?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please enter the name of your reporting team.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>supply_chain_operations</t>
+          <t>forecasting_team</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>supply_chain_operations</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>What are the names of the members of your forecasting team?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please list the names of the members of your forecasting team.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>supply_chain_operations_1</t>
+          <t>execution_team</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>risk</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>What is the name of your execution team?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please enter the name of your execution team.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,41 +628,49 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>supply_chain_operations_2</t>
+          <t>communication_frequency</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>operations_team</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>What is the frequency of your communication with your suppliers?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please describe the frequency of your communication with your suppliers.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>supply_chain_operations_3</t>
+          <t>review_frequency</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>risk_assess</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>How often do you review your supply chain operations plan?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please describe the frequency of your review of your supply chain operations plan.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,18 +682,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>supply_chain_operations_4</t>
+          <t>risk_score</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>communication</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>What is the overall risk score of your supply chain operations?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please enter the overall risk score of your supply chain operations.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,18 +709,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>supply_chain_operations_5</t>
+          <t>current_status</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>communication</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>What is the current status of your supply chain operations?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please describe the current status of your supply chain operations.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,41 +736,49 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>supply_chain_operations_6</t>
+          <t>primary_contact</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>communication</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Who is the primary contact person for your supply chain operations?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please enter the name and title of the primary contact person for your supply chain operations.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>overall_report_score</t>
+          <t>meeting_frequency</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>overall_score</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>What is the frequency of your meetings with your supply chain team?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please describe the frequency of your meetings with your supply chain team.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,18 +790,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>overall_risk_score</t>
+          <t>overall_score</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>overall_risk_score</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>What is the overall score of your supply chain operations?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please enter the overall score of your supply chain operations.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,18 +817,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>supply_chain_operations_7</t>
+          <t>inventory_management</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>overall_risk</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>What is the name of your inventory management team?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please enter the name of your inventory management team.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,18 +844,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>supply_chain_operations_8</t>
+          <t>planning_team</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>overall_risk_score</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>What is the name of your planning team?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Please enter the name of your planning team.</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -819,18 +871,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>overall_report_score_1</t>
+          <t>monitoring_team</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>overall_score</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>What is the name of your monitoring team?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Please enter the name of your monitoring team.</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -842,18 +898,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>supply_chain_operations_9</t>
+          <t>execution_team_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>overall_risk_score</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Execution Team 2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Please enter the name of your execution team.</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -865,18 +925,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>supply_chain_report_score_2</t>
+          <t>inventory_management_team</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>overall_score</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Inventory Management Team</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Please enter the name of your inventory management team.</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -888,18 +952,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>overall_risk_2</t>
+          <t>current_status_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>overall_risk</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>What is the current status of your supply chain operations score?</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Please describe the current status of your supply chain operations score.</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -911,179 +979,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>supply_chain_operations_10</t>
+          <t>overall_score_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>overall_risk_score</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>What is the overall score of your inventory management?</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Please enter the overall score of your inventory management.</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>overall_risk_score</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>overall_risk_score</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>supply_chain_operations_11</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>overall.score</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>overall_score_1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>overall_score</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>overall_risk_score</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>overall_risk_score</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>overall_report_score</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>overall_score</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>supply_chain_report_score</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>overall_score</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>overall_risk</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>overall_risk</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1009,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,85 +1037,272 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>supply_chain_operations_1_choices</t>
+          <t>forecasting_team_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'high'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'High'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>supply_chain_operations_1_choices</t>
+          <t>forecasting_team_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'medium'}</t>
+          <t>doe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Medium'}</t>
+          <t>Doe</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>supply_chain_operations_1_choices</t>
+          <t>forecasting_team_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'low'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Low'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>supply_chain_operations_2_choices</t>
+          <t>forecasting_team_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-.reporting_-_planning_-_forecasting_-_execution_-_monitoring</t>
+          <t>smith</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-.reporting - planning - forecasting - execution - monitoring</t>
+          <t>Smith</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>supply_chain_operations_2_choices</t>
+          <t>communication_frequency_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>communication_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>communication_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>communication_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>review_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>review_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>review_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>review_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>meeting_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>meeting_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>meeting_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>meeting_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
